--- a/public/documents/pieces-reponse-1/R1-rapprochement-caisse-factures.xlsx
+++ b/public/documents/pieces-reponse-1/R1-rapprochement-caisse-factures.xlsx
@@ -120,13 +120,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>non inventorié (aucune ligne à ce libellé)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -709,7 +709,11 @@
           <t>75</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>non inventorié (aucune ligne à ce libellé)</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>300</t>
@@ -747,7 +751,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>non inventorié (aucune ligne à ce libellé)</t>
+        </is>
+      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>150</t>
@@ -785,7 +793,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>non inventorié (aucune ligne à ce libellé)</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>0</t>
@@ -823,7 +835,11 @@
           <t>1 800</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>non inventorié (aucune ligne à ce libellé)</t>
+        </is>
+      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>225</t>
@@ -861,7 +877,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>non inventorié (aucune ligne à ce libellé)</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>0</t>
@@ -899,7 +919,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>non inventorié (aucune ligne à ce libellé)</t>
+        </is>
+      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>0</t>
@@ -981,7 +1005,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>non inventorié (aucune ligne à ce libellé)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1023,7 +1047,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>non inventorié (aucune ligne à ce libellé)</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1066,6 +1090,13 @@
       <c r="H17" s="9" t="inlineStr">
         <is>
           <t>NON : les achats couvrent 2,8 fois les ventes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Lecture de la colonne « Stock de clôture » : un chiffre est la quantité portée à l'inventaire physique de la clôture ; la mention « non inventorié (aucune ligne à ce libellé) » signifie que la référence ne figure à aucune ligne de cet inventaire, ce qui n'est pas un stock nul. Les deux vins blancs (Hautes Côtes de Beaune blanc, Hautes Côtes de Nuits blanc) ont été cherchés aux trois clôtures par libellé et par prix unitaire d'achat (9,95 € et 12,22 €) : ils n'y figurent sous aucun libellé.</t>
         </is>
       </c>
     </row>
@@ -1198,27 +1229,27 @@
       <c r="E6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Exercice 1</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>TOTAL imprime</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>5 400</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>4 683</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>somme des lignes : 5 400 et 4 683 ; addition exacte ; ecart imprime 717 cl (15,31 %), recalcule 717 cl (15,31 %)</t>
         </is>
@@ -1302,27 +1333,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Exercice 2</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>TOTAL imprime</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>6 300</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>18 260</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>somme des lignes : 6 300 et 18 260 ; addition exacte ; ecart imprime 11 960 cl (65,49 %), recalcule 11 960 cl (65,50 %)</t>
         </is>
@@ -1406,34 +1437,34 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Exercice 3</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>TOTAL imprime</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>6 300</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>18 260</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>somme des lignes : 6 300 et 18 260 ; addition exacte ; ecart imprime 11 960 cl (65,49 %), recalcule 11 960 cl (65,50 %)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Volumes de HC de Beaune rouge reellement enregistres en caisse (annexes C/D) : 2022-2023 = 7 218 cl ; 2023-2024 = 5 310 cl ; 2024-2025 = 4 683 cl</t>
         </is>
@@ -4499,7 +4530,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Objet</t>
         </is>
@@ -4511,7 +4542,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Achats</t>
         </is>
@@ -4523,7 +4554,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Exercice</t>
         </is>
@@ -4535,7 +4566,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Ventes caisse</t>
         </is>
@@ -4547,19 +4578,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Stocks</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>public/documents/inventaires/inventaires.json (inventaires physiques de cloture des 31/03/2023, 31/03/2024 et 31/03/2025).</t>
+          <t>public/documents/inventaires/inventaires.json (inventaires physiques de cloture des 31/03/2023, 31/03/2024 et 31/03/2025). La colonne "Stock de cloture" distingue deux situations que rien ne doit confondre : une quantite inventoriee, meme nulle, et une reference qui ne figure a aucune ligne de l'etat, portee "non inventorié (aucune ligne à ce libellé)". Le Hautes Cotes de Beaune rouge n'est ainsi inventorie qu'aux clotures du 31/03/2023 et du 31/03/2025 ; l'etat du 31/03/2024 ne le mentionne pas. Les deux vins BLANCS ont ete cherches aux trois clotures par libelle puis par prix unitaire d'achat (9,95 EUR le Hautes Cotes de Beaune blanc, 12,22 EUR le Hautes Cotes de Nuits blanc) : ils n'y figurent sous aucun libelle.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Tableaux p. 75</t>
         </is>
@@ -4571,7 +4602,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Genere par</t>
         </is>
